--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486443_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486443_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>R. COSIALLS BORRAS</t>
+          <t>F. COPES</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1.3668</v>
+        <v>1.4295</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5573</v>
+        <v>0.0868</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8095</v>
+        <v>1.3427</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.1716</v>
+        <v>-0.6878</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4986</v>
+        <v>-0.4623</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.6702</v>
+        <v>-0.2255</v>
       </c>
       <c r="J2" t="n">
-        <v>1.0637</v>
+        <v>0.5315</v>
       </c>
       <c r="K2" t="n">
-        <v>0.949</v>
+        <v>-0.5594</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1147</v>
+        <v>1.0909</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.2353</v>
+        <v>-1.2193</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.4504</v>
+        <v>0.09710000000000001</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.7849</v>
+        <v>-1.3164</v>
       </c>
       <c r="P2" t="n">
-        <v>1.7401</v>
+        <v>0.87</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R2" t="n">
-        <v>1.7401</v>
+        <v>1.9576</v>
       </c>
       <c r="S2" t="n">
-        <v>0.9283</v>
+        <v>0.8568</v>
       </c>
       <c r="T2" t="n">
-        <v>0.2331</v>
+        <v>0.2524</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6952</v>
+        <v>0.6044</v>
       </c>
       <c r="V2" t="n">
-        <v>-1.13</v>
+        <v>0.3904</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.7395</v>
+        <v>0.3904</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.3904</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>F. COPES</t>
+          <t>R. COSIALLS BORRAS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8022</v>
+        <v>1.1695</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.5405</v>
+        <v>0.5141</v>
       </c>
       <c r="F3" t="n">
-        <v>1.3427</v>
+        <v>0.6554</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.6878</v>
+        <v>-0.1716</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.4623</v>
+        <v>0.4986</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2255</v>
+        <v>-0.6702</v>
       </c>
       <c r="J3" t="n">
-        <v>0.5315</v>
+        <v>1.0637</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.5594</v>
+        <v>0.949</v>
       </c>
       <c r="L3" t="n">
-        <v>1.0909</v>
+        <v>0.1147</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.2193</v>
+        <v>-1.2353</v>
       </c>
       <c r="N3" t="n">
-        <v>0.09710000000000001</v>
+        <v>-0.4504</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.3164</v>
+        <v>-0.7849</v>
       </c>
       <c r="P3" t="n">
-        <v>0.87</v>
+        <v>1.7401</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.9576</v>
+        <v>1.7401</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2295</v>
+        <v>0.7309</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.3749</v>
+        <v>0.1899</v>
       </c>
       <c r="U3" t="n">
-        <v>0.6044</v>
+        <v>0.5411</v>
       </c>
       <c r="V3" t="n">
-        <v>0.3904</v>
+        <v>-1.13</v>
       </c>
       <c r="W3" t="n">
-        <v>0.3904</v>
+        <v>-0.7395</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-0.3904</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1777</v>
+        <v>0.5768</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.4017</v>
+        <v>0.1823</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5794</v>
+        <v>0.3945</v>
       </c>
       <c r="G4" t="n">
         <v>-2.1562</v>
@@ -766,13 +766,13 @@
         <v>1.5225</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.2963</v>
+        <v>0.1027</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.822</v>
+        <v>-0.2379</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5256</v>
+        <v>0.3407</v>
       </c>
       <c r="V4" t="n">
         <v>1.3252</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. SHELIST</t>
+          <t>M. TOWNES VILLAR</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.0919</v>
+        <v>-0.7085</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.7509</v>
+        <v>-0.3391</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.341</v>
+        <v>-0.3694</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.3987</v>
+        <v>2.4869</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.891</v>
+        <v>0.9975000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.5077</v>
+        <v>1.4894</v>
       </c>
       <c r="J5" t="n">
-        <v>-1.095</v>
+        <v>6.069</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.2862</v>
+        <v>1.6488</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1912</v>
+        <v>4.4202</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.3038</v>
+        <v>-3.5821</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3951</v>
+        <v>-0.6512</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.6989</v>
+        <v>-2.9309</v>
       </c>
       <c r="P5" t="n">
-        <v>1.0875</v>
+        <v>-3.6976</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.0875</v>
+        <v>-6.5252</v>
       </c>
       <c r="R5" t="n">
-        <v>2.1751</v>
+        <v>2.8276</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2193</v>
+        <v>0.307</v>
       </c>
       <c r="T5" t="n">
-        <v>0.3016</v>
+        <v>-0.0781</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0823</v>
+        <v>0.3851</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.1952</v>
       </c>
       <c r="W5" t="n">
-        <v>1.13</v>
+        <v>0.1952</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. TOWNES VILLAR</t>
+          <t>D. SHELIST</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.1508</v>
+        <v>-1.0928</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.9664</v>
+        <v>-0.9059</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.1845</v>
+        <v>-0.1869</v>
       </c>
       <c r="G6" t="n">
-        <v>2.4869</v>
+        <v>-2.3987</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9975000000000001</v>
+        <v>-0.891</v>
       </c>
       <c r="I6" t="n">
-        <v>1.4894</v>
+        <v>-1.5077</v>
       </c>
       <c r="J6" t="n">
-        <v>6.069</v>
+        <v>-1.095</v>
       </c>
       <c r="K6" t="n">
-        <v>1.6488</v>
+        <v>-1.2862</v>
       </c>
       <c r="L6" t="n">
-        <v>4.4202</v>
+        <v>0.1912</v>
       </c>
       <c r="M6" t="n">
-        <v>-3.5821</v>
+        <v>-1.3038</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.6512</v>
+        <v>0.3951</v>
       </c>
       <c r="O6" t="n">
-        <v>-2.9309</v>
+        <v>-1.6989</v>
       </c>
       <c r="P6" t="n">
-        <v>-3.6976</v>
+        <v>1.0875</v>
       </c>
       <c r="Q6" t="n">
-        <v>-6.5252</v>
+        <v>-1.0875</v>
       </c>
       <c r="R6" t="n">
-        <v>2.8276</v>
+        <v>2.1751</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1353</v>
+        <v>0.2184</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.7054</v>
+        <v>0.1466</v>
       </c>
       <c r="U6" t="n">
-        <v>0.5701000000000001</v>
+        <v>0.0718</v>
       </c>
       <c r="V6" t="n">
-        <v>0.1952</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0.1952</v>
+        <v>1.13</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>F. NWAOKORIE</t>
+          <t>D. DUSCAK</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.6059</v>
+        <v>-1.4365</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.1998</v>
+        <v>-1.7142</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5939</v>
+        <v>0.2777</v>
       </c>
       <c r="G7" t="n">
-        <v>-3.1316</v>
+        <v>-2.5147</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.4964</v>
+        <v>-0.9704</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.6351</v>
+        <v>-1.5443</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.5488</v>
+        <v>-1.061</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.6141</v>
+        <v>-0.8331</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.9347</v>
+        <v>-0.2279</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.5827</v>
+        <v>-1.4537</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.8823</v>
+        <v>-0.1372</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.7004</v>
+        <v>-1.3164</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.87</v>
+        <v>1.5225</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.3926</v>
+        <v>-0.2175</v>
       </c>
       <c r="R7" t="n">
-        <v>1.5225</v>
+        <v>1.7401</v>
       </c>
       <c r="S7" t="n">
-        <v>1.2658</v>
+        <v>-0.6395999999999999</v>
       </c>
       <c r="T7" t="n">
-        <v>0.6117</v>
+        <v>-0.6309</v>
       </c>
       <c r="U7" t="n">
-        <v>0.6541</v>
+        <v>-0.008699999999999999</v>
       </c>
       <c r="V7" t="n">
-        <v>1.13</v>
+        <v>0.1952</v>
       </c>
       <c r="W7" t="n">
-        <v>1.13</v>
+        <v>0.1952</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D. DUSCAK</t>
+          <t>A. FAURE RIBES</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.7507</v>
+        <v>-1.7152</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.6276</v>
+        <v>-1.8591</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.123</v>
+        <v>0.1439</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.5147</v>
+        <v>-0.8289</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.9704</v>
+        <v>-0.213</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.5443</v>
+        <v>-0.616</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.061</v>
+        <v>-0.1611</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.8331</v>
+        <v>-0.1611</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.2279</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.4537</v>
+        <v>-0.6679</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.1372</v>
+        <v>-0.0519</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.3164</v>
+        <v>-0.616</v>
       </c>
       <c r="P8" t="n">
-        <v>1.5225</v>
+        <v>-0.87</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.2175</v>
+        <v>-1.305</v>
       </c>
       <c r="R8" t="n">
-        <v>1.7401</v>
+        <v>0.435</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.9538</v>
+        <v>-0.0162</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5444</v>
+        <v>-0.3929</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4094</v>
+        <v>0.3767</v>
       </c>
       <c r="V8" t="n">
-        <v>0.1952</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0.1952</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. FAURE RIBES</t>
+          <t>F. NWAOKORIE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.2606</v>
+        <v>-2.3552</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.2196</v>
+        <v>-2.7333</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.0411</v>
+        <v>0.3781</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.8289</v>
+        <v>-3.1316</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.213</v>
+        <v>-1.4964</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.616</v>
+        <v>-1.6351</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.1611</v>
+        <v>-1.5488</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.1611</v>
+        <v>-0.6141</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>-0.9347</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.6679</v>
+        <v>-1.5827</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.0519</v>
+        <v>-0.8823</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.616</v>
+        <v>-0.7004</v>
       </c>
       <c r="P9" t="n">
         <v>-0.87</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.305</v>
+        <v>-2.3926</v>
       </c>
       <c r="R9" t="n">
-        <v>0.435</v>
+        <v>1.5225</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5617</v>
+        <v>0.5164</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.7534999999999999</v>
+        <v>0.0781</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1918</v>
+        <v>0.4383</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.8266</v>
+        <v>-2.4237</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.175</v>
+        <v>-3.9263</v>
       </c>
       <c r="F11" t="n">
-        <v>1.3485</v>
+        <v>1.5026</v>
       </c>
       <c r="G11" t="n">
         <v>-3.5608</v>
@@ -1312,13 +1312,13 @@
         <v>1.305</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.9608</v>
+        <v>-0.5579</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.0274</v>
+        <v>-0.7786999999999999</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0667</v>
+        <v>0.2208</v>
       </c>
       <c r="V11" t="n">
         <v>1.695</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.1137</v>
+        <v>-4.8699</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.1933</v>
+        <v>-4.7953</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0795</v>
+        <v>-0.0746</v>
       </c>
       <c r="G12" t="n">
         <v>-6.0916</v>
@@ -1390,13 +1390,13 @@
         <v>1.9576</v>
       </c>
       <c r="S12" t="n">
-        <v>1.4559</v>
+        <v>0.6997</v>
       </c>
       <c r="T12" t="n">
-        <v>1.0587</v>
+        <v>0.4567</v>
       </c>
       <c r="U12" t="n">
-        <v>0.3972</v>
+        <v>0.243</v>
       </c>
       <c r="V12" t="n">
         <v>0.7395</v>
@@ -1423,19 +1423,19 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-14.8367</v>
+        <v>-13.8092</v>
       </c>
       <c r="E13" t="n">
-        <v>-17.6233</v>
+        <v>-16.5958</v>
       </c>
       <c r="F13" t="n">
-        <v>2.7864</v>
+        <v>2.7865</v>
       </c>
       <c r="G13" t="n">
         <v>-19.2327</v>
       </c>
       <c r="H13" t="n">
-        <v>-7.6346</v>
+        <v>-7.634600000000001</v>
       </c>
       <c r="I13" t="n">
         <v>-11.5982</v>
@@ -1459,7 +1459,7 @@
         <v>-13.1641</v>
       </c>
       <c r="P13" t="n">
-        <v>3.608224830031759e-16</v>
+        <v>1.387778780781446e-16</v>
       </c>
       <c r="Q13" t="n">
         <v>-17.4004</v>
@@ -1468,13 +1468,13 @@
         <v>17.4006</v>
       </c>
       <c r="S13" t="n">
-        <v>0.9854000000000002</v>
+        <v>2.0127</v>
       </c>
       <c r="T13" t="n">
-        <v>-2.079</v>
+        <v>-1.0513</v>
       </c>
       <c r="U13" t="n">
-        <v>3.0644</v>
+        <v>3.0642</v>
       </c>
       <c r="V13" t="n">
         <v>3.4105</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>10.1174</v>
+        <v>10.5465</v>
       </c>
       <c r="E14" t="n">
-        <v>5.4822</v>
+        <v>5.7058</v>
       </c>
       <c r="F14" t="n">
-        <v>4.6352</v>
+        <v>4.8407</v>
       </c>
       <c r="G14" t="n">
         <v>11.1897</v>
@@ -1546,13 +1546,13 @@
         <v>2.8276</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.4198</v>
+        <v>0.009299999999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.9469</v>
+        <v>-0.7234</v>
       </c>
       <c r="U14" t="n">
-        <v>0.5272</v>
+        <v>0.7327</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>6.0926</v>
+        <v>5.593</v>
       </c>
       <c r="E15" t="n">
-        <v>3.0773</v>
+        <v>2.742</v>
       </c>
       <c r="F15" t="n">
-        <v>3.0153</v>
+        <v>2.851</v>
       </c>
       <c r="G15" t="n">
         <v>6.7721</v>
@@ -1624,13 +1624,13 @@
         <v>2.6101</v>
       </c>
       <c r="S15" t="n">
-        <v>0.9932</v>
+        <v>0.4936</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.2019</v>
+        <v>-0.5371</v>
       </c>
       <c r="U15" t="n">
-        <v>1.1951</v>
+        <v>1.0307</v>
       </c>
       <c r="V15" t="n">
         <v>-1.8902</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.3922</v>
+        <v>4.9496</v>
       </c>
       <c r="E16" t="n">
-        <v>1.8994</v>
+        <v>2.1229</v>
       </c>
       <c r="F16" t="n">
-        <v>2.4928</v>
+        <v>2.8267</v>
       </c>
       <c r="G16" t="n">
         <v>2.1031</v>
@@ -1702,13 +1702,13 @@
         <v>1.0875</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.2552</v>
+        <v>0.3022</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.262</v>
+        <v>-0.0384</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0067</v>
+        <v>0.3407</v>
       </c>
       <c r="V16" t="n">
         <v>1.6743</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.534</v>
+        <v>4.3895</v>
       </c>
       <c r="E17" t="n">
-        <v>0.7665</v>
+        <v>0.9901</v>
       </c>
       <c r="F17" t="n">
-        <v>2.7675</v>
+        <v>3.3995</v>
       </c>
       <c r="G17" t="n">
         <v>3.2238</v>
@@ -1780,13 +1780,13 @@
         <v>1.7401</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.6903</v>
+        <v>0.1652</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.3305</v>
+        <v>-0.1069</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3598</v>
+        <v>0.2722</v>
       </c>
       <c r="V17" t="n">
         <v>-0.7395</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.0927</v>
+        <v>-0.1042</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.137</v>
+        <v>-0.0252</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0443</v>
+        <v>-0.079</v>
       </c>
       <c r="G18" t="n">
         <v>-0.216</v>
@@ -1858,13 +1858,13 @@
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1233</v>
+        <v>0.1118</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.137</v>
+        <v>-0.0252</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2603</v>
+        <v>0.137</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. ARMUS</t>
+          <t>T. BORG</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.9991</v>
+        <v>-0.1999</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.4139</v>
+        <v>-3.1085</v>
       </c>
       <c r="F19" t="n">
-        <v>1.4148</v>
+        <v>2.9085</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.1844</v>
+        <v>1.6626</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.2895</v>
+        <v>1.0705</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1052</v>
+        <v>0.5921</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.2392</v>
+        <v>1.4787</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.4687</v>
+        <v>0.4443</v>
       </c>
       <c r="L19" t="n">
-        <v>0.2295</v>
+        <v>1.0343</v>
       </c>
       <c r="M19" t="n">
-        <v>0.0548</v>
+        <v>0.1839</v>
       </c>
       <c r="N19" t="n">
-        <v>0.1792</v>
+        <v>0.6262</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.1243</v>
+        <v>-0.4423</v>
       </c>
       <c r="P19" t="n">
-        <v>1.0875</v>
+        <v>-2.6101</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.305</v>
+        <v>-5.4377</v>
       </c>
       <c r="R19" t="n">
-        <v>2.3926</v>
+        <v>2.8276</v>
       </c>
       <c r="S19" t="n">
-        <v>0.2277</v>
+        <v>-0.1872</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.0649</v>
+        <v>-0.4747</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2926</v>
+        <v>0.2875</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.13</v>
+        <v>0.9347</v>
       </c>
       <c r="W19" t="n">
-        <v>0.1952</v>
+        <v>1.3252</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.3252</v>
+        <v>-0.3904</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>T. BORG</t>
+          <t>X. OROZ URIA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.347</v>
+        <v>-0.61</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.4437</v>
+        <v>-0.3476</v>
       </c>
       <c r="F20" t="n">
-        <v>2.0967</v>
+        <v>-0.2624</v>
       </c>
       <c r="G20" t="n">
-        <v>1.6626</v>
+        <v>0.5684</v>
       </c>
       <c r="H20" t="n">
-        <v>1.0705</v>
+        <v>1.025</v>
       </c>
       <c r="I20" t="n">
-        <v>0.5921</v>
+        <v>-0.4566</v>
       </c>
       <c r="J20" t="n">
-        <v>1.4787</v>
+        <v>1.1581</v>
       </c>
       <c r="K20" t="n">
-        <v>0.4443</v>
+        <v>1.0434</v>
       </c>
       <c r="L20" t="n">
-        <v>1.0343</v>
+        <v>0.1147</v>
       </c>
       <c r="M20" t="n">
-        <v>0.1839</v>
+        <v>-0.5898</v>
       </c>
       <c r="N20" t="n">
-        <v>0.6262</v>
+        <v>-0.0184</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.4423</v>
+        <v>-0.5714</v>
       </c>
       <c r="P20" t="n">
-        <v>-2.6101</v>
+        <v>-0.6525</v>
       </c>
       <c r="Q20" t="n">
-        <v>-5.4377</v>
+        <v>-1.5225</v>
       </c>
       <c r="R20" t="n">
-        <v>2.8276</v>
+        <v>0.87</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.3342</v>
+        <v>0.6042</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.8099</v>
+        <v>0.0168</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.5243</v>
+        <v>0.5873</v>
       </c>
       <c r="V20" t="n">
-        <v>0.9347</v>
+        <v>-1.13</v>
       </c>
       <c r="W20" t="n">
-        <v>1.3252</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.3904</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X. OROZ URIA</t>
+          <t>M. ARMUS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.3974</v>
+        <v>-1.1532</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.6829</v>
+        <v>-2.8609</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.7145</v>
+        <v>1.7077</v>
       </c>
       <c r="G21" t="n">
-        <v>0.5684</v>
+        <v>-1.1844</v>
       </c>
       <c r="H21" t="n">
-        <v>1.025</v>
+        <v>-1.2895</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.4566</v>
+        <v>0.1052</v>
       </c>
       <c r="J21" t="n">
-        <v>1.1581</v>
+        <v>-1.2392</v>
       </c>
       <c r="K21" t="n">
-        <v>1.0434</v>
+        <v>-1.4687</v>
       </c>
       <c r="L21" t="n">
-        <v>0.1147</v>
+        <v>0.2295</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.5898</v>
+        <v>0.0548</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.0184</v>
+        <v>0.1792</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.5714</v>
+        <v>-0.1243</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.6525</v>
+        <v>1.0875</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.5225</v>
+        <v>-1.305</v>
       </c>
       <c r="R21" t="n">
-        <v>0.87</v>
+        <v>2.3926</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1833</v>
+        <v>0.0736</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3184</v>
+        <v>-0.5119</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1352</v>
+        <v>0.5855</v>
       </c>
       <c r="V21" t="n">
         <v>-1.13</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>0.1952</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.13</v>
+        <v>-1.3252</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.4424</v>
+        <v>-1.2009</v>
       </c>
       <c r="E22" t="n">
         <v>-1.9086</v>
       </c>
       <c r="F22" t="n">
-        <v>0.4662</v>
+        <v>0.7077</v>
       </c>
       <c r="G22" t="n">
         <v>-1.057</v>
@@ -2170,13 +2170,13 @@
         <v>0.435</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.6029</v>
+        <v>-0.3614</v>
       </c>
       <c r="T22" t="n">
         <v>-0.274</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3289</v>
+        <v>-0.08740000000000001</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A. MUÑOZ BORCHERS</t>
+          <t>M. HERON</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.963</v>
+        <v>-2.1209</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.1236</v>
+        <v>-2.6376</v>
       </c>
       <c r="F23" t="n">
-        <v>1.1606</v>
+        <v>0.5167</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.7529</v>
+        <v>-1.0766</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.0277</v>
+        <v>-0.173</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.7252</v>
+        <v>-0.9036999999999999</v>
       </c>
       <c r="J23" t="n">
-        <v>-2.6237</v>
+        <v>-0.2558</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.9368</v>
+        <v>-0.3706</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.6869</v>
+        <v>0.1147</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.1292</v>
+        <v>-0.8208</v>
       </c>
       <c r="N23" t="n">
-        <v>0.9091</v>
+        <v>0.1976</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.0383</v>
+        <v>-1.0184</v>
       </c>
       <c r="P23" t="n">
-        <v>1.305</v>
+        <v>-1.5225</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.435</v>
+        <v>-2.3926</v>
       </c>
       <c r="R23" t="n">
-        <v>1.7401</v>
+        <v>0.87</v>
       </c>
       <c r="S23" t="n">
-        <v>0.6148</v>
+        <v>0.4783</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.0649</v>
+        <v>0.0108</v>
       </c>
       <c r="U23" t="n">
-        <v>0.6797</v>
+        <v>0.4675</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>M. HERON</t>
+          <t>A. MUÑOZ BORCHERS</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.0579</v>
+        <v>-2.2726</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.3023</v>
+        <v>-3.4589</v>
       </c>
       <c r="F24" t="n">
-        <v>0.2444</v>
+        <v>1.1863</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.0766</v>
+        <v>-2.7529</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.173</v>
+        <v>-1.0277</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.9036999999999999</v>
+        <v>-1.7252</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.2558</v>
+        <v>-2.6237</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.3706</v>
+        <v>-1.9368</v>
       </c>
       <c r="L24" t="n">
-        <v>0.1147</v>
+        <v>-0.6869</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.8208</v>
+        <v>-0.1292</v>
       </c>
       <c r="N24" t="n">
-        <v>0.1976</v>
+        <v>0.9091</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.0184</v>
+        <v>-1.0383</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.5225</v>
+        <v>1.305</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.3926</v>
+        <v>-0.435</v>
       </c>
       <c r="R24" t="n">
-        <v>0.87</v>
+        <v>1.7401</v>
       </c>
       <c r="S24" t="n">
-        <v>0.5412</v>
+        <v>0.3052</v>
       </c>
       <c r="T24" t="n">
-        <v>0.3461</v>
+        <v>-0.4002</v>
       </c>
       <c r="U24" t="n">
-        <v>0.1952</v>
+        <v>0.7054</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>14.8367</v>
+        <v>17.8169</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.7866</v>
+        <v>-2.786499999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>17.6233</v>
+        <v>20.6034</v>
       </c>
       <c r="G25" t="n">
         <v>19.2328</v>
@@ -2389,7 +2389,7 @@
         <v>3.4651</v>
       </c>
       <c r="N25" t="n">
-        <v>5.0314</v>
+        <v>5.031400000000001</v>
       </c>
       <c r="O25" t="n">
         <v>-1.566</v>
@@ -2404,13 +2404,13 @@
         <v>17.4006</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.9855000000000002</v>
+        <v>1.9948</v>
       </c>
       <c r="T25" t="n">
-        <v>-3.0643</v>
+        <v>-3.0642</v>
       </c>
       <c r="U25" t="n">
-        <v>2.079</v>
+        <v>5.0591</v>
       </c>
       <c r="V25" t="n">
         <v>-3.4107</v>
@@ -2419,7 +2419,7 @@
         <v>1.9109</v>
       </c>
       <c r="X25" t="n">
-        <v>-5.3215</v>
+        <v>-5.321499999999999</v>
       </c>
     </row>
   </sheetData>
